--- a/accor/data/scenarios.xlsx
+++ b/accor/data/scenarios.xlsx
@@ -1751,2196 +1751,2196 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>c8c6e6032b1ff74c83207cfcec36a070e96070dbca27fe14aaf698544691eb27</t>
+          <t>026f978d18bc9050267ca1b7e3fd4ba5a2ac46c976ec5a893e7b6eb67372a371</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>["BAUME LEVRES", "JEU"]</t>
+          <t>["BAUME LEVRES", "NUXE"]</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>026f978d18bc9050267ca1b7e3fd4ba5a2ac46c976ec5a893e7b6eb67372a371</t>
+          <t>9a0e950d868bbcda2298343c91396aac2a147aac6ac6ee799217b6ab6adc1c4d</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>["BAUME LEVRES", "NUXE"]</t>
+          <t>["BERET", "TROUSSE"]</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>9a0e950d868bbcda2298343c91396aac2a147aac6ac6ee799217b6ab6adc1c4d</t>
+          <t>bc2a06d5b49ada1cab3df7e39dce65bae41e917c8a62efd1a4cadb25f7ff4629</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>["BERET", "TROUSSE"]</t>
+          <t>["BIERE", "CHAMPAGNE"]</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>bc2a06d5b49ada1cab3df7e39dce65bae41e917c8a62efd1a4cadb25f7ff4629</t>
+          <t>29d50ca688dbdc59f87af8861b6145270049c691f1a31b597cffd8eaf6f6b3d8</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>["BIERE", "CHAMPAGNE"]</t>
+          <t>["BIERE", "LIQUEUR"]</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>29d50ca688dbdc59f87af8861b6145270049c691f1a31b597cffd8eaf6f6b3d8</t>
+          <t>8fbd2da9c83bc0f94e16f0ba032ac5387d542a4aed436c05d29ec7efb7ae7362</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>["BIERE", "LIQUEUR"]</t>
+          <t>["BIERE", "NESPRESSO"]</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>8fbd2da9c83bc0f94e16f0ba032ac5387d542a4aed436c05d29ec7efb7ae7362</t>
+          <t>16f3756c2f7b0294cf6aee27fef4dcd6b3b15ecd6c8f149436f6ae3e1f0d5972</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>["BIERE", "NESPRESSO"]</t>
+          <t>["BIERE", "SAN BENEDETTO"]</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>16f3756c2f7b0294cf6aee27fef4dcd6b3b15ecd6c8f149436f6ae3e1f0d5972</t>
+          <t>3af2453000c8c39e2228e724bd56ca43ec5fddd038ffb150e37bc55eefd18a9a</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>["BIERE", "SAN BENEDETTO"]</t>
+          <t>["BIERE", "SANDWICH"]</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>3af2453000c8c39e2228e724bd56ca43ec5fddd038ffb150e37bc55eefd18a9a</t>
+          <t>4067a1fd7c517b6a8ed14b06740dcfa30b12db628e22e8220d008e7be0a659a1</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>["BIERE", "SANDWICH"]</t>
+          <t>["BISCUIT", "PATES"]</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>4067a1fd7c517b6a8ed14b06740dcfa30b12db628e22e8220d008e7be0a659a1</t>
+          <t>3eda903f11bf46598e97ee58c79359f1101068540b8cfd4b2132f952b1adff87</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>["BISCUIT", "PATES"]</t>
+          <t>["BOB ARTENGO", "POLAIRE"]</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>3eda903f11bf46598e97ee58c79359f1101068540b8cfd4b2132f952b1adff87</t>
+          <t>02e3165f2acc57c814590abb569aa061bcfc5674f224cf45b4f69a3be99c5202</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>["BOB ARTENGO", "POLAIRE"]</t>
+          <t>["BOITE DE CARAMELS", "CABLE"]</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>02e3165f2acc57c814590abb569aa061bcfc5674f224cf45b4f69a3be99c5202</t>
+          <t>ca4f8fc54cc0a6528638a514d63eab807c510a3f43f5d1b2b1006856aa445b88</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>["BOITE DE CARAMELS", "CABLE"]</t>
+          <t>["BOITE DE CARAMELS", "PORTE CLE"]</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ca4f8fc54cc0a6528638a514d63eab807c510a3f43f5d1b2b1006856aa445b88</t>
+          <t>aed71bed30d35a66277a831dabd562b18f06af2415ba78206facaf904fb210d9</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>["BOITE DE CARAMELS", "PORTE CLE"]</t>
+          <t>["BOITE DE CARAMELS", "SET DE THE"]</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>aed71bed30d35a66277a831dabd562b18f06af2415ba78206facaf904fb210d9</t>
+          <t>ed9d467bcf719d6f4564275de0208ac3d33612b32ba2edd85e3e48138b299f8f</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>["BOITE DE CARAMELS", "SET DE THE"]</t>
+          <t>["BRASSARDS", "LIVRE"]</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ed9d467bcf719d6f4564275de0208ac3d33612b32ba2edd85e3e48138b299f8f</t>
+          <t>c5432cfd92226c64d7369dd0c9fb55516cf5d28b9694fec4f2d1cb4b1863f3da</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>["BRASSARDS", "LIVRE"]</t>
+          <t>["BRASSARDS", "MINI BALLON"]</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>c5432cfd92226c64d7369dd0c9fb55516cf5d28b9694fec4f2d1cb4b1863f3da</t>
+          <t>1c5802814c4c768a7685b5cdd9aab12cc3fc9fd54bfb31143fa56fd91058dffa</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>["BRASSARDS", "MINI BALLON"]</t>
+          <t>["CABLE", "CHARGEUR"]</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1c5802814c4c768a7685b5cdd9aab12cc3fc9fd54bfb31143fa56fd91058dffa</t>
+          <t>97bef6401a5bf1369256a93a075af898679a65ca0988efafd83f174ee5cffb37</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>["CABLE", "CHARGEUR"]</t>
+          <t>["CABLE", "SOUVENIR"]</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>97bef6401a5bf1369256a93a075af898679a65ca0988efafd83f174ee5cffb37</t>
+          <t>3c0c04e9db0ee5c58f79bf7e977f911c545af7b0d6bd54c8fbad28a265d557d6</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>["CABLE", "SOUVENIR"]</t>
+          <t>["CACAHUETES", "GRAINES"]</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>3c0c04e9db0ee5c58f79bf7e977f911c545af7b0d6bd54c8fbad28a265d557d6</t>
+          <t>1ef47edaeb3ff3aab29b89e50f46d60210a220e71466b3e281b8ae8be45862bc</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>["CACAHUETES", "GRAINES"]</t>
+          <t>["CACTUS PIQUANT", "CARROT CAKE"]</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1ef47edaeb3ff3aab29b89e50f46d60210a220e71466b3e281b8ae8be45862bc</t>
+          <t>74f052b5d4d5d05e867930b1aee306d308e45577f9432e7db2d0e5fde4ca1481</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>["CACTUS PIQUANT", "CARROT CAKE"]</t>
+          <t>["CARTE POSTALE", "TROUSSE"]</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>74f052b5d4d5d05e867930b1aee306d308e45577f9432e7db2d0e5fde4ca1481</t>
+          <t>5e0666684f4d9be4b80cce4b315025ce38d962abf175f8a28f4fae5929ba74f1</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>["CARTE POSTALE", "TROUSSE"]</t>
+          <t>["CASQUETTE", "CHAUSSETTES"]</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>5e0666684f4d9be4b80cce4b315025ce38d962abf175f8a28f4fae5929ba74f1</t>
+          <t>dbd2d82ba90f81ef9037e24f710e0db139cb877f2e7c2814bcfafc5e6b54e78e</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>["CASQUETTE", "CHAUSSETTES"]</t>
+          <t>["CASQUETTE", "LE CHERCHE"]</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>dbd2d82ba90f81ef9037e24f710e0db139cb877f2e7c2814bcfafc5e6b54e78e</t>
+          <t>512a4ff253b26a97e04a02dcbc56f62cd23c045b78edb680aaee1aeb56085a67</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>["CASQUETTE", "LE CHERCHE"]</t>
+          <t>["CHALETS NOEL", "DRAGIBUS"]</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>512a4ff253b26a97e04a02dcbc56f62cd23c045b78edb680aaee1aeb56085a67</t>
+          <t>b365d0029cc4612344725790a70458c504e26f814bcfdccc510b59f502d2ad6e</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>["CHALETS NOEL", "DRAGIBUS"]</t>
+          <t>["CHALETS NOEL", "GRAINES"]</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>b365d0029cc4612344725790a70458c504e26f814bcfdccc510b59f502d2ad6e</t>
+          <t>02a7d8ec060eb1ae1f8f3ff011c960bd12faf500447f52ae46ccca869208fce7</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>["CHALETS NOEL", "GRAINES"]</t>
+          <t>["CHALETS NOEL", "SOUVENIR"]</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>02a7d8ec060eb1ae1f8f3ff011c960bd12faf500447f52ae46ccca869208fce7</t>
+          <t>892ec60d87fdfa65ec282b78086297b88f00ff961b20826c545ec91a5c05d87f</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>["CHALETS NOEL", "SOUVENIR"]</t>
+          <t>["CHATOUILLE", "GEL HYDROALCOOLIQUE"]</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>892ec60d87fdfa65ec282b78086297b88f00ff961b20826c545ec91a5c05d87f</t>
+          <t>e3d387ad498901d191facef62492bd6b96164d600280bf1c321f8469dc3a222e</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>["CHATOUILLE", "GEL HYDROALCOOLIQUE"]</t>
+          <t>["CHATOUILLE", "GRAINES"]</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>e3d387ad498901d191facef62492bd6b96164d600280bf1c321f8469dc3a222e</t>
+          <t>39c6ee1d311e573a0c94652b22255eed2dda0692aee0d6a31aa02472fd65ae78</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>["CHATOUILLE", "GRAINES"]</t>
+          <t>["CHATOUILLE", "PLAT"]</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>39c6ee1d311e573a0c94652b22255eed2dda0692aee0d6a31aa02472fd65ae78</t>
+          <t>c3fdd23d96d746dc4ea8a893f0e12d10d5c958f3ca2b48ff7690486a64e4064f</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>["CHATOUILLE", "PLAT"]</t>
+          <t>["CHIPS", "SALADE BOWL"]</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>c3fdd23d96d746dc4ea8a893f0e12d10d5c958f3ca2b48ff7690486a64e4064f</t>
+          <t>d5d657aa9300d264d5f9c814990d2ee1e1a93af8fd8308aeea6cefbcecd518eb</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>["CHIPS", "SALADE BOWL"]</t>
+          <t>["CHIPS", "SANDWICH"]</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>d5d657aa9300d264d5f9c814990d2ee1e1a93af8fd8308aeea6cefbcecd518eb</t>
+          <t>a27d39562cbf8ba7a62c626245e22471978af2b2a2101e1f489e4f078bec4c29</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>["CHIPS", "SANDWICH"]</t>
+          <t>["CHOCOLAT", "KIT COUVERTS"]</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>a27d39562cbf8ba7a62c626245e22471978af2b2a2101e1f489e4f078bec4c29</t>
+          <t>128900ffca505fb8cbdacd9e4dddc038f6edaf30ca3807b2d5e5bb67bc0d5aae</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>["CHOCOLAT", "KIT COUVERTS"]</t>
+          <t>["CHOCOLAT", "TRAITEUR"]</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>128900ffca505fb8cbdacd9e4dddc038f6edaf30ca3807b2d5e5bb67bc0d5aae</t>
+          <t>3d182208c6a38ea2001f983dbc0ea39fde81c9a312a3b4bccb7aba8f8e02437d</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>["CHOCOLAT", "TRAITEUR"]</t>
+          <t>["CHOCOLAT", "YAOURT"]</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>3d182208c6a38ea2001f983dbc0ea39fde81c9a312a3b4bccb7aba8f8e02437d</t>
+          <t>d89d6c5ecb3e0d0ad069466a5ed4f00397e5a023f67f734ccb461e9631d0a1cb</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>["CHOCOLAT", "YAOURT"]</t>
+          <t>["COCA COLA", "COCA COLA CHERRY"]</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>d89d6c5ecb3e0d0ad069466a5ed4f00397e5a023f67f734ccb461e9631d0a1cb</t>
+          <t>f58ec51d5734d09ebdcfbc4505616882311891faba25b120dd539977d8e762c2</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>["COCA COLA", "COCA COLA CHERRY"]</t>
+          <t>["COCA COLA", "COCA COLA ZERO"]</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>f58ec51d5734d09ebdcfbc4505616882311891faba25b120dd539977d8e762c2</t>
+          <t>c7f0d779a9e45240f7e3a07be377950a878a45e05c56b04edf7dcf9692b89abf</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>["COCA COLA", "COCA COLA ZERO"]</t>
+          <t>["COCA COLA CHERRY", "COCA COLA ZERO"]</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>c7f0d779a9e45240f7e3a07be377950a878a45e05c56b04edf7dcf9692b89abf</t>
+          <t>b57066fa0a53f94ad9b17a7300e99d83bc8e016c9672bde0c816ba0c5870130a</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>["COCA COLA CHERRY", "COCA COLA ZERO"]</t>
+          <t>["CONFITURE", "SOUPE"]</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>b57066fa0a53f94ad9b17a7300e99d83bc8e016c9672bde0c816ba0c5870130a</t>
+          <t>a873a5823e68b45bc559a435fd8b0748570ec2b9e6e9dee6cbea6d1fe02b704d</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>["CONFITURE", "SOUPE"]</t>
+          <t>["COSMETIQUE", "DEODORANT"]</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>a873a5823e68b45bc559a435fd8b0748570ec2b9e6e9dee6cbea6d1fe02b704d</t>
+          <t>385f3ff98b520e8a6619d3add88509e756460c977097dfe09fb8586a80e6d539</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>["COSMETIQUE", "DEODORANT"]</t>
+          <t>["CREME ANTI", "CREME SOLAIRE"]</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>385f3ff98b520e8a6619d3add88509e756460c977097dfe09fb8586a80e6d539</t>
+          <t>2bdc15fbfcee71bf3861e80231e45b637e10fbee32636562f41a2b9beaf6252a</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>["CREME ANTI", "CREME SOLAIRE"]</t>
+          <t>["CREME SOLAIRE", "RITUALS"]</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2bdc15fbfcee71bf3861e80231e45b637e10fbee32636562f41a2b9beaf6252a</t>
+          <t>87076e2f651042b312d96831c14bce466f93479a11250258cb4002e16a9c2d81</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>["CREME SOLAIRE", "RITUALS"]</t>
+          <t>["CRUNCH", "FRAISE TAGADA"]</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>87076e2f651042b312d96831c14bce466f93479a11250258cb4002e16a9c2d81</t>
+          <t>5aaadac0d882f5bf14355145f07466276463ba781c3634dd9b4df69e0b34128d</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>["CRUNCH", "FRAISE TAGADA"]</t>
+          <t>["DEODORANT", "FRAISE TAGADA"]</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>5aaadac0d882f5bf14355145f07466276463ba781c3634dd9b4df69e0b34128d</t>
+          <t>f8838c6a3a1691a79473077d43526528a348d6d21b1caa53ebcbb6a5f46aaca2</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>["DEODORANT", "FRAISE TAGADA"]</t>
+          <t>["DEODORANT", "GANTS"]</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>f8838c6a3a1691a79473077d43526528a348d6d21b1caa53ebcbb6a5f46aaca2</t>
+          <t>c97f7d2d52fdc8427c651838b03ad11ca2cc2caec96dda162caf1e4c5801790b</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>["DEODORANT", "GANTS"]</t>
+          <t>["DEODORANT", "HYGIENE FEMININE"]</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>c97f7d2d52fdc8427c651838b03ad11ca2cc2caec96dda162caf1e4c5801790b</t>
+          <t>88287716814314a555c018e1f586e8e73808713f0b042daf17e8b8e149eff082</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>["DEODORANT", "HYGIENE FEMININE"]</t>
+          <t>["DESSERT", "KIT COUVERTS"]</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>88287716814314a555c018e1f586e8e73808713f0b042daf17e8b8e149eff082</t>
+          <t>cfe355443fa07f1096c9616d783cc5cc13f8b74bc6a6f99dcd846d8fe034c001</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>["DESSERT", "KIT COUVERTS"]</t>
+          <t>["DESSERT", "MPG HOUMOUS"]</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>cfe355443fa07f1096c9616d783cc5cc13f8b74bc6a6f99dcd846d8fe034c001</t>
+          <t>d0368a5e7deead3bf394b7dacf2d6d9cd513be06ec8576351a35ec578e8f7f6a</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>["DESSERT", "MPG HOUMOUS"]</t>
+          <t>["DESSERT", "MPG MOUSSE"]</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>d0368a5e7deead3bf394b7dacf2d6d9cd513be06ec8576351a35ec578e8f7f6a</t>
+          <t>0a636c37e363536aa2a5d4384b781fcd14a8f29b0d725f857ced1abe6c31a79c</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>["DESSERT", "MPG MOUSSE"]</t>
+          <t>["DESSERT", "SALADE BOWL"]</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>0a636c37e363536aa2a5d4384b781fcd14a8f29b0d725f857ced1abe6c31a79c</t>
+          <t>42b2be98a9b40e617e276be20591e4f655a6307bd2770673802d66f4e3d3ade3</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>["DESSERT", "SALADE BOWL"]</t>
+          <t>["DESSERT", "TRAITEUR"]</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>42b2be98a9b40e617e276be20591e4f655a6307bd2770673802d66f4e3d3ade3</t>
+          <t>49e89c845427b949972d7286e1680c3db9c3a37d2b17ea0bcc3b79cf3b893554</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>["DESSERT", "TRAITEUR"]</t>
+          <t>["DRAGIBUS", "FRAISE TAGADA"]</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>49e89c845427b949972d7286e1680c3db9c3a37d2b17ea0bcc3b79cf3b893554</t>
+          <t>7d556902c7774bde8b2ae5c2e754a4d3f32caa9289cf01524710cd9ea3e58157</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>["DRAGIBUS", "FRAISE TAGADA"]</t>
+          <t>["EAU", "RED BULL"]</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>7d556902c7774bde8b2ae5c2e754a4d3f32caa9289cf01524710cd9ea3e58157</t>
+          <t>c2ac18469cfc7e0b434f27caedf1ffa419637814a2af2880a1210fbb96930e62</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>["EAU", "RED BULL"]</t>
+          <t>["EVIAN", "SPRAY FACIAL"]</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>c2ac18469cfc7e0b434f27caedf1ffa419637814a2af2880a1210fbb96930e62</t>
+          <t>e2f01cae5d4b54eebcbd625700d001cd7ffe1db493b8724a1ce8649f9898b809</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>["EVIAN", "SPRAY FACIAL"]</t>
+          <t>["FLOCONS DE MEGEVE", "MERINGUES MYRTILLES"]</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>e2f01cae5d4b54eebcbd625700d001cd7ffe1db493b8724a1ce8649f9898b809</t>
+          <t>a34b178d7f06628a9e673588041d4646c74a6c7c0f72bc75316b182195801ff1</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>["FLOCONS DE MEGEVE", "MERINGUES MYRTILLES"]</t>
+          <t>["FRAISE TAGADA", "LIMONADE"]</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>a34b178d7f06628a9e673588041d4646c74a6c7c0f72bc75316b182195801ff1</t>
+          <t>8c89e15b9752f53ccbbafb0c01adb2eb7e1696c723579850379a6a0d3fae6195</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>["FRAISE TAGADA", "LIMONADE"]</t>
+          <t>["GANTS", "TOUR DE COU"]</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>8c89e15b9752f53ccbbafb0c01adb2eb7e1696c723579850379a6a0d3fae6195</t>
+          <t>984b7ba08914ba2529c12250e4eec99fe6681d4a25035a7c3b8c02973e745327</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>["GANTS", "TOUR DE COU"]</t>
+          <t>["GEL HYDROALCOOLIQUE", "PARFUM"]</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>984b7ba08914ba2529c12250e4eec99fe6681d4a25035a7c3b8c02973e745327</t>
+          <t>1f72c777a03af710100c5b89595363497c2aedcee290e0e84e92eacb92b63cd2</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>["GEL HYDROALCOOLIQUE", "PARFUM"]</t>
+          <t>["GOURDE", "ISOTHERME"]</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1f72c777a03af710100c5b89595363497c2aedcee290e0e84e92eacb92b63cd2</t>
+          <t>f6602f2b0106ee30c3076a33ad3c3ef626780bfc6238a6bd64d005ebac50a00a</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>["GOURDE", "ISOTHERME"]</t>
+          <t>["GOURDE", "TIRE BOUCHON"]</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>f6602f2b0106ee30c3076a33ad3c3ef626780bfc6238a6bd64d005ebac50a00a</t>
+          <t>79ef3959f58e0f428f936b64216805c101ab4051fbb6749041adc9b3ff3569c6</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>["GOURDE", "TIRE BOUCHON"]</t>
+          <t>["HYGIENE FEMININE", "SERVIETTES LOVE"]</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>79ef3959f58e0f428f936b64216805c101ab4051fbb6749041adc9b3ff3569c6</t>
+          <t>6ff0c4d78887896b388c335aea4535e91975ffae40660462fd2c54c725c68d83</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>["HYGIENE FEMININE", "SERVIETTES LOVE"]</t>
+          <t>["JUS", "RED BULL"]</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>6ff0c4d78887896b388c335aea4535e91975ffae40660462fd2c54c725c68d83</t>
+          <t>479552241d2f395051012323fc8a2dfe5de9d755ed00741ad4c4fdae2bd11c61</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>["JUS", "RED BULL"]</t>
+          <t>["JUS", "SOUVENIR"]</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>479552241d2f395051012323fc8a2dfe5de9d755ed00741ad4c4fdae2bd11c61</t>
+          <t>c3be1a2f2909cf81a63010cb09dd4d5b4a81ddeb0f7181ed76ac0780a4b03518</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>["JUS", "SOUVENIR"]</t>
+          <t>["KINDER", "KINDER BUENO"]</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>c3be1a2f2909cf81a63010cb09dd4d5b4a81ddeb0f7181ed76ac0780a4b03518</t>
+          <t>dd643105956ff846243e001d2d17b83bfde62909c210fca27372424e312b7a91</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>["KINDER", "KINDER BUENO"]</t>
+          <t>["LIMONADE", "SPRITE"]</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>dd643105956ff846243e001d2d17b83bfde62909c210fca27372424e312b7a91</t>
+          <t>e9a2a9fe6a3f0433c8bc3620d00fa47c794fa9ebc9e734134ddae04556b72ca6</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>["LIMONADE", "SPRITE"]</t>
+          <t>["MIEL", "PATES"]</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>e9a2a9fe6a3f0433c8bc3620d00fa47c794fa9ebc9e734134ddae04556b72ca6</t>
+          <t>943e82efbd09becd5c08e3c4c001c6e656dd3557da66e7443dbc5a73329eb73b</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>["MIEL", "PATES"]</t>
+          <t>["MPG HOUMOUS", "PORTE CLE"]</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>943e82efbd09becd5c08e3c4c001c6e656dd3557da66e7443dbc5a73329eb73b</t>
+          <t>745982e55f9de07d43d4e40db0829616a682706dd3f1865816b08be118ec2480</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>["MPG HOUMOUS", "PORTE CLE"]</t>
+          <t>["MPG HOUMOUS", "SALADE BOWL"]</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>745982e55f9de07d43d4e40db0829616a682706dd3f1865816b08be118ec2480</t>
+          <t>78c334d5612d948d4cd2dc4861fe40ef27a79e79e2797bc55a95b998d61b2589</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>["MPG HOUMOUS", "SALADE BOWL"]</t>
+          <t>["NUXE", "PONCHO"]</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>78c334d5612d948d4cd2dc4861fe40ef27a79e79e2797bc55a95b998d61b2589</t>
+          <t>176cc7c531ba2962dde194d0cc4b2e5b1b0b952149a40cba142ffdf378f24727</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>["NUXE", "PONCHO"]</t>
+          <t>["PATES", "SANDWICH"]</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>176cc7c531ba2962dde194d0cc4b2e5b1b0b952149a40cba142ffdf378f24727</t>
+          <t>33f514620fbc3bc914ad5491209de4d11e0f5f7a6d6dacb3b9dbf363f0e3bf50</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>["PATES", "SANDWICH"]</t>
+          <t>["PETIT SAUCISSON", "TRAITEUR"]</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>33f514620fbc3bc914ad5491209de4d11e0f5f7a6d6dacb3b9dbf363f0e3bf50</t>
+          <t>b2d965d976e2ee1579b1f97f6229098d807f885e1fcd1b10b5119e4900779c0c</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>["PETIT SAUCISSON", "TRAITEUR"]</t>
+          <t>["PLAT", "SOUPE"]</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>b2d965d976e2ee1579b1f97f6229098d807f885e1fcd1b10b5119e4900779c0c</t>
+          <t>4c2b982956e1cf386d714a41c27e74fa264ad00c8d7115e4b0c548753c60c389</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>["PLAT", "SOUPE"]</t>
+          <t>["POICAMOLE", "SOUPE"]</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>4c2b982956e1cf386d714a41c27e74fa264ad00c8d7115e4b0c548753c60c389</t>
+          <t>0815ac0357eee5cc379ea66147a6819c411eb8c94ba55d887b5488b50089c623</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>["POICAMOLE", "SOUPE"]</t>
+          <t>["POLAIRE", "TOUR DE COU"]</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>0815ac0357eee5cc379ea66147a6819c411eb8c94ba55d887b5488b50089c623</t>
+          <t>6f6bb33f78add358da9f8a93f408e1d196a0e33bb2c85662bb62ecad9081c41c</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>["POLAIRE", "TOUR DE COU"]</t>
+          <t>["PONCHO", "PORTE CLE"]</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>6f6bb33f78add358da9f8a93f408e1d196a0e33bb2c85662bb62ecad9081c41c</t>
+          <t>f166b611bb37b0016ada830646a727bbd5d585edbd57f3523fa400cbf9b505b9</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>["PONCHO", "PORTE CLE"]</t>
+          <t>["PONCHO", "PRESERVATIF"]</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>f166b611bb37b0016ada830646a727bbd5d585edbd57f3523fa400cbf9b505b9</t>
+          <t>0d35b26ec35528b5ce5c5ec566a45d5271c0c8d2bec3cd3fcea22a7935dc1e16</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>["PONCHO", "PRESERVATIF"]</t>
+          <t>["RESPIRE GEL", "RESPIRE HUILE"]</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>0d35b26ec35528b5ce5c5ec566a45d5271c0c8d2bec3cd3fcea22a7935dc1e16</t>
+          <t>d200acb73a0b2ce19430eb9970ae8732cecf074c6fe59210977a3da3c3f95753</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>["RESPIRE GEL", "RESPIRE HUILE"]</t>
+          <t>["SALADE BOWL", "SANDWICH"]</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>d200acb73a0b2ce19430eb9970ae8732cecf074c6fe59210977a3da3c3f95753</t>
+          <t>d3ff9460b5f032fd5dd55b28b0069baa6be17fe67f595d736bc8f8c339f64acd</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>["SALADE BOWL", "SANDWICH"]</t>
+          <t>["TRAITEUR", "YAOURT"]</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>d3ff9460b5f032fd5dd55b28b0069baa6be17fe67f595d736bc8f8c339f64acd</t>
+          <t>c9f6c3423d12e9b7c802442a89567268e4e44e815723d3f59602dce7103b1ff5</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>["TRAITEUR", "YAOURT"]</t>
+          <t>["ANTI MOUSTIQUE", "DEODORANT", "HYGIENE FEMININE"]</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>c9f6c3423d12e9b7c802442a89567268e4e44e815723d3f59602dce7103b1ff5</t>
+          <t>5aa145fddc74eb8d48f74b3fc3b14d18e6e0a7df163b402307148fdb73e13f80</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>["ANTI MOUSTIQUE", "DEODORANT", "HYGIENE FEMININE"]</t>
+          <t>["APERITIF SALE", "BISCUIT", "PATES"]</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>5aa145fddc74eb8d48f74b3fc3b14d18e6e0a7df163b402307148fdb73e13f80</t>
+          <t>973d4497a40488185e4a8bf98abb84467ed691ef39dbd39438301489e042abae</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>["APERITIF SALE", "BISCUIT", "PATES"]</t>
+          <t>["APERITIF SALE", "MIEL", "PATES"]</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>973d4497a40488185e4a8bf98abb84467ed691ef39dbd39438301489e042abae</t>
+          <t>7955f0b5b2605c7f72e2c049f7b65d27f44652627b2ff45f826819446b3d72f6</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>["APERITIF SALE", "MIEL", "PATES"]</t>
+          <t>["ASSORTIMENT DE GUIMAUVE", "DESSERT", "PATES"]</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>7955f0b5b2605c7f72e2c049f7b65d27f44652627b2ff45f826819446b3d72f6</t>
+          <t>23ce3cd5b4ef3bd7fd6bffb6b9a07610ff66f1cfe62df14e5792e9711f18108c</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>["ASSORTIMENT DE GUIMAUVE", "DESSERT", "PATES"]</t>
+          <t>["ASSORTIMENT DE GUIMAUVE", "FLOCONS DE MEGEVE", "GRAINES"]</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>23ce3cd5b4ef3bd7fd6bffb6b9a07610ff66f1cfe62df14e5792e9711f18108c</t>
+          <t>97a259fd9f7b1106e14bc52d19ced7456dbac6a140e55051fb0211ab99f460b1</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>["ASSORTIMENT DE GUIMAUVE", "FLOCONS DE MEGEVE", "GRAINES"]</t>
+          <t>["BAIES DE GOJI", "BARRE", "CAFE CHOCOLAT"]</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>97a259fd9f7b1106e14bc52d19ced7456dbac6a140e55051fb0211ab99f460b1</t>
+          <t>feab1584f4d95f86734c355ef51e5d275a249657be4e754fe5a35b28ce819e59</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>["BAIES DE GOJI", "BARRE", "CAFE CHOCOLAT"]</t>
+          <t>["BAIES DE GOJI", "BISCUIT", "PATES"]</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>feab1584f4d95f86734c355ef51e5d275a249657be4e754fe5a35b28ce819e59</t>
+          <t>8006b4f44f9886644736f0dbd5a43a773ff76571f4ba5604b853f4c7f8ac3e8f</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>["BAIES DE GOJI", "BISCUIT", "PATES"]</t>
+          <t>["BAIES DE GOJI", "CHOCOLAT", "YAOURT"]</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>8006b4f44f9886644736f0dbd5a43a773ff76571f4ba5604b853f4c7f8ac3e8f</t>
+          <t>a9800434338df9768c19c91bddf109e746e707442e6abe420d4d0f7ede36c970</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>["BAIES DE GOJI", "CHOCOLAT", "YAOURT"]</t>
+          <t>["BAM CO", "BARRE", "SNICKERS"]</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>a9800434338df9768c19c91bddf109e746e707442e6abe420d4d0f7ede36c970</t>
+          <t>71db36093bd4d4b97e18b3b826b649e62b1f6e0caadf4caf0ceaca38f5a8ee92</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>["BAM CO", "BARRE", "SNICKERS"]</t>
+          <t>["BAM CO", "GULA", "SALADE BOWL"]</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>71db36093bd4d4b97e18b3b826b649e62b1f6e0caadf4caf0ceaca38f5a8ee92</t>
+          <t>24927a3354a171d313c937dfb36ebdd8a91419c1d821abd8ccb9eeeb448eff7a</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>["BAM CO", "GULA", "SALADE BOWL"]</t>
+          <t>["BAM CO", "GULA", "SNICKERS"]</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>24927a3354a171d313c937dfb36ebdd8a91419c1d821abd8ccb9eeeb448eff7a</t>
+          <t>e2d61a7f4de43e1e35927e7c04deee3082213bc7f14f0225e17fea98a36bf6e2</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>["BAM CO", "GULA", "SNICKERS"]</t>
+          <t>["BARQUETTE DE FRAISE", "CONFITURE", "CRUNCH"]</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>e2d61a7f4de43e1e35927e7c04deee3082213bc7f14f0225e17fea98a36bf6e2</t>
+          <t>afe483ea2c8e15b2eaafdbb5f0d53f22cbca187c3730b2f225a8482c31b0c0b8</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>["BARQUETTE DE FRAISE", "CONFITURE", "CRUNCH"]</t>
+          <t>["BARQUETTE DE FRAISE", "CONFITURE", "PLAT"]</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>afe483ea2c8e15b2eaafdbb5f0d53f22cbca187c3730b2f225a8482c31b0c0b8</t>
+          <t>b961103d16962a0695c9d305b2fb488ad9b3be4ca8a3034be16ef4683d2e3df5</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>["BARQUETTE DE FRAISE", "CONFITURE", "PLAT"]</t>
+          <t>["BARQUETTE DE FRAISE", "POICAMOLE", "SOUPE"]</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>b961103d16962a0695c9d305b2fb488ad9b3be4ca8a3034be16ef4683d2e3df5</t>
+          <t>4bd5b93f5d5f6430c4ac7e93748d2d2002d85bd6b7c01eb66393a4c27567f424</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>["BARQUETTE DE FRAISE", "POICAMOLE", "SOUPE"]</t>
+          <t>["BARRE", "BISCUIT", "GRAINES"]</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>4bd5b93f5d5f6430c4ac7e93748d2d2002d85bd6b7c01eb66393a4c27567f424</t>
+          <t>8d8d990aa1b6c6c09fe17c20964758ce126de03f104d11b19e0d7acd406f57ab</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>["BARRE", "BISCUIT", "GRAINES"]</t>
+          <t>["BARRE", "CRUNCH", "TRAITEUR"]</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>8d8d990aa1b6c6c09fe17c20964758ce126de03f104d11b19e0d7acd406f57ab</t>
+          <t>9da2febed9dc44bd5a090454f7001cd1a59104bcbedf52893ede71d7d91b802a</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>["BARRE", "CRUNCH", "TRAITEUR"]</t>
+          <t>["BARRE", "GEL HYDROALCOOLIQUE", "GRAINES"]</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>9da2febed9dc44bd5a090454f7001cd1a59104bcbedf52893ede71d7d91b802a</t>
+          <t>50a207aab1e42f145304bd17d7ce3f6ce970f6892f5ba13ee92b8ce75942efa8</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>["BARRE", "GEL HYDROALCOOLIQUE", "GRAINES"]</t>
+          <t>["BARRE", "SNICKERS", "SPECIAL K"]</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>50a207aab1e42f145304bd17d7ce3f6ce970f6892f5ba13ee92b8ce75942efa8</t>
+          <t>f3f2f2617cfc6e817380fba870fbb9a73afd06c549eac128f87cb5afdedee718</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>["BARRE", "SNICKERS", "SPECIAL K"]</t>
+          <t>["BATTERIE DE SECOURS", "GEL HYDROALCOOLIQUE", "KIT DENTAIRE"]</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>f3f2f2617cfc6e817380fba870fbb9a73afd06c549eac128f87cb5afdedee718</t>
+          <t>b91801d04d5a2b6feaf7f4736c0a04eee48dacf2439125a4312e119597743f23</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>["BATTERIE DE SECOURS", "GEL HYDROALCOOLIQUE", "KIT DENTAIRE"]</t>
+          <t>["BAUME LEVRES", "COSMETIQUE", "GEL HYDROALCOOLIQUE"]</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>b91801d04d5a2b6feaf7f4736c0a04eee48dacf2439125a4312e119597743f23</t>
+          <t>5a5a01ba951a1ee0487482210d7209860e6826cd51ab0aa59fbd3bba595b4b79</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>["BAUME LEVRES", "COSMETIQUE", "GEL HYDROALCOOLIQUE"]</t>
+          <t>["BAUME LEVRES", "RESPIRE GEL", "RESPIRE HUILE"]</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>5a5a01ba951a1ee0487482210d7209860e6826cd51ab0aa59fbd3bba595b4b79</t>
+          <t>01d2997cfaa6f9fac70aaa13bea9c54f4be4f38283da5dfb644e929278ae3b66</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>["BAUME LEVRES", "RESPIRE GEL", "RESPIRE HUILE"]</t>
+          <t>["BERET", "CASQUETTE", "TROUSSE"]</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>01d2997cfaa6f9fac70aaa13bea9c54f4be4f38283da5dfb644e929278ae3b66</t>
+          <t>558e65d1a8fba4c59d74d19eca8e643b4f833fece93dc00b1b6900e41abde364</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>["BERET", "CASQUETTE", "TROUSSE"]</t>
+          <t>["BIERE", "CHAMPAGNE", "HEINEKEN"]</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>558e65d1a8fba4c59d74d19eca8e643b4f833fece93dc00b1b6900e41abde364</t>
+          <t>90a5ffc7bb173786fbf88590dcfd7d6847377faf3a34b416b71ff11c1b042ef0</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>["BIERE", "CHAMPAGNE", "HEINEKEN"]</t>
+          <t>["BIERE", "JUS", "SOUVENIR"]</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>90a5ffc7bb173786fbf88590dcfd7d6847377faf3a34b416b71ff11c1b042ef0</t>
+          <t>1976a6a7f46d335d539032c3815ad975f36086761d244cdc74cb7d05f5b405d7</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>["BIERE", "JUS", "SOUVENIR"]</t>
+          <t>["BIERE", "NESPRESSO", "ORANGINA"]</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>1976a6a7f46d335d539032c3815ad975f36086761d244cdc74cb7d05f5b405d7</t>
+          <t>881b2caf5bd6750608bd2cf2fc0d6a8c8fd96ba9faf566a325f2d18744f83ead</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>["BIERE", "NESPRESSO", "ORANGINA"]</t>
+          <t>["BIERE", "OASIS", "SAN BENEDETTO"]</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>881b2caf5bd6750608bd2cf2fc0d6a8c8fd96ba9faf566a325f2d18744f83ead</t>
+          <t>ff2ce3109288579c427ab5a142ee94b4bca4653add19fd4bfeee871833cfe7bf</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>["BIERE", "OASIS", "SAN BENEDETTO"]</t>
+          <t>["BISCUIT", "CHIPS", "PATES"]</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>ff2ce3109288579c427ab5a142ee94b4bca4653add19fd4bfeee871833cfe7bf</t>
+          <t>ec883305a2add4caa130f81d7db3d469a1b04d9ee92cf631d94f755860f1895e</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>["BISCUIT", "CHIPS", "PATES"]</t>
+          <t>["BISCUIT", "TRAITEUR", "YAOURT"]</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>ec883305a2add4caa130f81d7db3d469a1b04d9ee92cf631d94f755860f1895e</t>
+          <t>42aed7c6947e9f2f5d45e8674cea2f807612572309b444830a10233a2fe41b64</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>["BISCUIT", "TRAITEUR", "YAOURT"]</t>
+          <t>["BOB ARTENGO", "CHAUSSETTES", "POLAIRE"]</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>42aed7c6947e9f2f5d45e8674cea2f807612572309b444830a10233a2fe41b64</t>
+          <t>7a3207732f62cbf0b1896129f90c5875a214c9fef669467e93b8013a3504c4da</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>["BOB ARTENGO", "CHAUSSETTES", "POLAIRE"]</t>
+          <t>["BOB ARTENGO", "POLAIRE", "TOUR DE COU"]</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>7a3207732f62cbf0b1896129f90c5875a214c9fef669467e93b8013a3504c4da</t>
+          <t>1b10fadad735daf71a250fdf6fe86454267217aee76b99a5f1ae01dddecd0765</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>["BOB ARTENGO", "POLAIRE", "TOUR DE COU"]</t>
+          <t>["BOITE DE CARAMELS", "BOITE MTL", "SET DE THE"]</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>1b10fadad735daf71a250fdf6fe86454267217aee76b99a5f1ae01dddecd0765</t>
+          <t>75aad44da88887d81d92603176de6fcfd2c8ae66856f8e3a8728967d8ea8f9be</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>["BOITE DE CARAMELS", "BOITE MTL", "SET DE THE"]</t>
+          <t>["BOITE DE CARAMELS", "CABLE", "PRESERVATIF"]</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>75aad44da88887d81d92603176de6fcfd2c8ae66856f8e3a8728967d8ea8f9be</t>
+          <t>28dd17f4474218df23f9e8720566d659d83b1f2ccf2c6ddc87773b25272a4bae</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>["BOITE DE CARAMELS", "CABLE", "PRESERVATIF"]</t>
+          <t>["BOITE DE CARAMELS", "PORTE CLE", "SET DE THE"]</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>28dd17f4474218df23f9e8720566d659d83b1f2ccf2c6ddc87773b25272a4bae</t>
+          <t>f6950b078827a705a2e435fc06d92a94dcf9516ba2b32399073fcb3c1e455778</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>["BOITE DE CARAMELS", "PORTE CLE", "SET DE THE"]</t>
+          <t>["BONNET", "GANTS", "TOUR DE COU"]</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>f6950b078827a705a2e435fc06d92a94dcf9516ba2b32399073fcb3c1e455778</t>
+          <t>da2ac7a6c87cea6d70503c69e63be5322ced6b20922ec7d1e27a0cb6c3b53ea8</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>["BONNET", "GANTS", "TOUR DE COU"]</t>
+          <t>["BOUEE", "CREME ANTI", "CREME SOLAIRE"]</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>da2ac7a6c87cea6d70503c69e63be5322ced6b20922ec7d1e27a0cb6c3b53ea8</t>
+          <t>975ac6fa3fbaeeb0e76f22609ef683e448eb18ae4a0d8bcf91ed7044a692539d</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>["BOUEE", "CREME ANTI", "CREME SOLAIRE"]</t>
+          <t>["BRASSARDS", "CHAUFFERETTES", "LIVRE"]</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>975ac6fa3fbaeeb0e76f22609ef683e448eb18ae4a0d8bcf91ed7044a692539d</t>
+          <t>0c0af9a6702efcae201d742ab72ba416955f42e9434dce7c51da3a5306c3147a</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>["BRASSARDS", "CHAUFFERETTES", "LIVRE"]</t>
+          <t>["BRASSARDS", "MINI BALLON", "POLAIRE"]</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>0c0af9a6702efcae201d742ab72ba416955f42e9434dce7c51da3a5306c3147a</t>
+          <t>3f8addb318b5ab201b963e36d512004eb7002aa1a5dc4723e4a179ffdb630201</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>["BRASSARDS", "MINI BALLON", "POLAIRE"]</t>
+          <t>["CABLE", "CHALETS NOEL", "SOUVENIR"]</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>3f8addb318b5ab201b963e36d512004eb7002aa1a5dc4723e4a179ffdb630201</t>
+          <t>76520a721f3197f2a09546744bd212ad62f59799ea9fe7357c9c9edfdb45d82b</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>["CABLE", "CHALETS NOEL", "SOUVENIR"]</t>
+          <t>["CABLE", "CHARGEUR", "SOUVENIR"]</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>76520a721f3197f2a09546744bd212ad62f59799ea9fe7357c9c9edfdb45d82b</t>
+          <t>e5c87de2dade930567396e7fa1821fd07025629e5390136610b708886fc990e8</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>["CABLE", "CHARGEUR", "SOUVENIR"]</t>
+          <t>["CABLE", "CHARGEUR", "TIRE BOUCHON"]</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>e5c87de2dade930567396e7fa1821fd07025629e5390136610b708886fc990e8</t>
+          <t>11e5ff3dbbb4ed419170be3e337943d5a0d58f2f9610f2e73f14ba7eef60f8c7</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>["CABLE", "CHARGEUR", "TIRE BOUCHON"]</t>
+          <t>["CABLE", "PONCHO", "PRESERVATIF"]</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>11e5ff3dbbb4ed419170be3e337943d5a0d58f2f9610f2e73f14ba7eef60f8c7</t>
+          <t>8cb6324af6c4c059ced1445c0c30d33851d3ab182c6d0eaf2fbf2fc5c79ecd97</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>["CABLE", "PONCHO", "PRESERVATIF"]</t>
+          <t>["CACAHUETES", "CHALETS NOEL", "GRAINES"]</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>8cb6324af6c4c059ced1445c0c30d33851d3ab182c6d0eaf2fbf2fc5c79ecd97</t>
+          <t>262155c36aee4049a365573964f81da9cbaaa685c59afb7f6df404aaf754506d</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>["CACAHUETES", "CHALETS NOEL", "GRAINES"]</t>
+          <t>["CACAHUETES", "GRAINES", "SOUPE"]</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>262155c36aee4049a365573964f81da9cbaaa685c59afb7f6df404aaf754506d</t>
+          <t>61106974e284a339d0d7acb5de0f09174a17ec5f93877d7d25f6fd878cefd3b4</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>["CACAHUETES", "GRAINES", "SOUPE"]</t>
+          <t>["CACTUS PIQUANT", "CARROT CAKE", "SET DE THE"]</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>61106974e284a339d0d7acb5de0f09174a17ec5f93877d7d25f6fd878cefd3b4</t>
+          <t>84a3c3ebb46b95e4281dce14609139725c1a48d9068abb6cf436f81c7552ad1a</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>["CACTUS PIQUANT", "CARROT CAKE", "SET DE THE"]</t>
+          <t>["CARROT CAKE", "DESSERT", "MPG MOUSSE"]</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>84a3c3ebb46b95e4281dce14609139725c1a48d9068abb6cf436f81c7552ad1a</t>
+          <t>02c164a12c3899f3e80a2ad139fa8b2c71252a74cd201148b72b08411c805039</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>["CARROT CAKE", "DESSERT", "MPG MOUSSE"]</t>
+          <t>["CARTE POSTALE", "PATES", "TROUSSE"]</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>02c164a12c3899f3e80a2ad139fa8b2c71252a74cd201148b72b08411c805039</t>
+          <t>04bbbc9f799bab3b3b7863217261d17b724e6ae371feb3411612e5a9696c1e42</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>["CARTE POSTALE", "PATES", "TROUSSE"]</t>
+          <t>["CASQUETTE", "CHAUSSETTES", "VESTE"]</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>04bbbc9f799bab3b3b7863217261d17b724e6ae371feb3411612e5a9696c1e42</t>
+          <t>96d8f63abe3d1b7c97616f6cc2875f99a87158c3c17cef8c7b656529f50e078b</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>["CASQUETTE", "CHAUSSETTES", "VESTE"]</t>
+          <t>["CASQUETTE", "LE CHERCHE", "ORAL B"]</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>96d8f63abe3d1b7c97616f6cc2875f99a87158c3c17cef8c7b656529f50e078b</t>
+          <t>c5965a28fa83fab3fad8c3074b521642f0b7602b064c27520c8981b4a58e4543</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>["CASQUETTE", "LE CHERCHE", "ORAL B"]</t>
+          <t>["CHALETS NOEL", "DRAGIBUS", "FRAISE TAGADA"]</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>c5965a28fa83fab3fad8c3074b521642f0b7602b064c27520c8981b4a58e4543</t>
+          <t>ea6b971644d07da6306c655e589dfbf54bd50a451b26bb1571f242a7e034b22f</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>["CHALETS NOEL", "DRAGIBUS", "FRAISE TAGADA"]</t>
+          <t>["CHALETS NOEL", "GRAINES", "SAN BENEDETTO"]</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>ea6b971644d07da6306c655e589dfbf54bd50a451b26bb1571f242a7e034b22f</t>
+          <t>1c375902e9d9aff24334c9c2c7492a4bde86b4e42e2186ad3a96ad53d48641b1</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>["CHALETS NOEL", "GRAINES", "SAN BENEDETTO"]</t>
+          <t>["CHATOUILLE", "GEL HYDROALCOOLIQUE", "GRAINES"]</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>1c375902e9d9aff24334c9c2c7492a4bde86b4e42e2186ad3a96ad53d48641b1</t>
+          <t>cb5be144132d862190186842d4596e6fbf18f78114333ce79e9743bb50dc6620</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>["CHATOUILLE", "GEL HYDROALCOOLIQUE", "GRAINES"]</t>
+          <t>["CHATOUILLE", "GRAINES", "PLAT"]</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>cb5be144132d862190186842d4596e6fbf18f78114333ce79e9743bb50dc6620</t>
+          <t>7539f9cf64426e95c70037acf4032e4db574de61c2943efb18df7ac75a0abe35</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>["CHATOUILLE", "GRAINES", "PLAT"]</t>
+          <t>["CHATOUILLE", "LE CLUB", "PLAT"]</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>7539f9cf64426e95c70037acf4032e4db574de61c2943efb18df7ac75a0abe35</t>
+          <t>fe5fb050b9e5e01880c5d84705cf927f8d091a15220ce290850a5eabfbda92b2</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>["CHATOUILLE", "LE CLUB", "PLAT"]</t>
+          <t>["CHIPS", "PATES", "SANDWICH"]</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>fe5fb050b9e5e01880c5d84705cf927f8d091a15220ce290850a5eabfbda92b2</t>
+          <t>3d942b6b719e1b2627833c28f333f7b1f53975e9068fb53a3881eb369ad0ac63</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>["CHIPS", "PATES", "SANDWICH"]</t>
+          <t>["CHIPS", "SALADE BOWL", "TRAITEUR"]</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>3d942b6b719e1b2627833c28f333f7b1f53975e9068fb53a3881eb369ad0ac63</t>
+          <t>02a45aaeb625d728b09c9fe405e11126838311b5a24941dc59428054f060f6a9</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>["CHIPS", "SALADE BOWL", "TRAITEUR"]</t>
+          <t>["CHOCOLAT", "KIT COUVERTS", "TRAITEUR"]</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>02a45aaeb625d728b09c9fe405e11126838311b5a24941dc59428054f060f6a9</t>
+          <t>1bd1bcc2b6bb5e445a7e5708636213548727d5201443aca079bdc49953b425f0</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>["CHOCOLAT", "KIT COUVERTS", "TRAITEUR"]</t>
+          <t>["CHOCOLAT", "TRAITEUR", "YAOURT"]</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>1bd1bcc2b6bb5e445a7e5708636213548727d5201443aca079bdc49953b425f0</t>
+          <t>e83f225b87ca1f3844e5ee306027d2bcbaf70471ddead855bb7108c370910565</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>["CHOCOLAT", "TRAITEUR", "YAOURT"]</t>
+          <t>["COCA COLA", "COCA COLA CHERRY", "COCA COLA ZERO"]</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>e83f225b87ca1f3844e5ee306027d2bcbaf70471ddead855bb7108c370910565</t>
+          <t>db28b432cd5a066a7fe8871cb98e7ef35554cff83fba5ead09e1050fc40fe4ad</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>["COCA COLA", "COCA COLA CHERRY", "COCA COLA ZERO"]</t>
+          <t>["CONFITURE", "SOUPE", "TARTINABLE MAQUEREAU"]</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>db28b432cd5a066a7fe8871cb98e7ef35554cff83fba5ead09e1050fc40fe4ad</t>
+          <t>c3520228412c09220460723d338eba724c3d3c0cec5a9c99c1bfcdbfad97bba5</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>["CONFITURE", "SOUPE", "TARTINABLE MAQUEREAU"]</t>
+          <t>["CRUNCH", "DEODORANT", "FRAISE TAGADA"]</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>c3520228412c09220460723d338eba724c3d3c0cec5a9c99c1bfcdbfad97bba5</t>
+          <t>1923679093f42519a73055939fcc37f679c3d82538406b89dd3824eb14f48e61</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>["CRUNCH", "DEODORANT", "FRAISE TAGADA"]</t>
+          <t>["CRUNCH", "FRAISE TAGADA", "KINDER"]</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>1923679093f42519a73055939fcc37f679c3d82538406b89dd3824eb14f48e61</t>
+          <t>ef46b39757d55a809adc05107c11a43e0b67fb585607f859af1a0c426aca0dcc</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>["CRUNCH", "FRAISE TAGADA", "KINDER"]</t>
+          <t>["CRUNCH", "PETIT SAUCISSON", "TRAITEUR"]</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>ef46b39757d55a809adc05107c11a43e0b67fb585607f859af1a0c426aca0dcc</t>
+          <t>d9d9bb1fef242b7656236b07235e87d13a1fc5d27b26045fc106ed597a8ce57e</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>["CRUNCH", "PETIT SAUCISSON", "TRAITEUR"]</t>
+          <t>["DEODORANT", "DIVERS", "HYGIENE FEMININE"]</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>d9d9bb1fef242b7656236b07235e87d13a1fc5d27b26045fc106ed597a8ce57e</t>
+          <t>9d4c7fc7bf34af47b48d2fc215b4473953c24b3ff5194b4bd80ffffcb2cf74c2</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>["DEODORANT", "DIVERS", "HYGIENE FEMININE"]</t>
+          <t>["DEODORANT", "FRAISE TAGADA", "GANTS"]</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>9d4c7fc7bf34af47b48d2fc215b4473953c24b3ff5194b4bd80ffffcb2cf74c2</t>
+          <t>47a10bef1e7dfe95264f2de011e11b1c791501cca4d247651324939ba075a8d5</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>["DEODORANT", "FRAISE TAGADA", "GANTS"]</t>
+          <t>["DEODORANT", "GANTS", "HYGIENE FEMININE"]</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>47a10bef1e7dfe95264f2de011e11b1c791501cca4d247651324939ba075a8d5</t>
+          <t>f441df8493c3fab2bddd77626dcfa623e09a01f967ca25b8fec0770c5604f9ff</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>["DEODORANT", "GANTS", "HYGIENE FEMININE"]</t>
+          <t>["DEODORANT", "RESPIRE GEL", "RESPIRE HUILE"]</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>f441df8493c3fab2bddd77626dcfa623e09a01f967ca25b8fec0770c5604f9ff</t>
+          <t>e518a3f52f134308ec4d78743471a95317954a67ff80209c97e11cbc42b62356</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>["DEODORANT", "RESPIRE GEL", "RESPIRE HUILE"]</t>
+          <t>["DESSERT", "MPG HOUMOUS", "MPG MOUSSE"]</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>e518a3f52f134308ec4d78743471a95317954a67ff80209c97e11cbc42b62356</t>
+          <t>3279fb6f37abf672dfd51ee0637d5540bbcccb44b5f6026fa67acdc4355f5636</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>["DESSERT", "MPG HOUMOUS", "MPG MOUSSE"]</t>
+          <t>["DESSERT", "MPG HOUMOUS", "PORTE CLE"]</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>3279fb6f37abf672dfd51ee0637d5540bbcccb44b5f6026fa67acdc4355f5636</t>
+          <t>fc71dc16d31df822df94363cbf77f8a34dc37264cd004fb9785f2f8160e358ee</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>["DESSERT", "MPG HOUMOUS", "PORTE CLE"]</t>
+          <t>["DESSERT", "SALADE BOWL", "TRAITEUR"]</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>fc71dc16d31df822df94363cbf77f8a34dc37264cd004fb9785f2f8160e358ee</t>
+          <t>1837b7c1ed489dfc164edb827ec3a003e36995e2387d0de68a871836553d5641</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>["DESSERT", "SALADE BOWL", "TRAITEUR"]</t>
+          <t>["DESSERT", "SOUPE", "TRAITEUR"]</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>1837b7c1ed489dfc164edb827ec3a003e36995e2387d0de68a871836553d5641</t>
+          <t>dffbd7228ef97383d8a99eac08a8bdb3bdeb12ee78ae43181baed195c5979ac7</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>["DESSERT", "SOUPE", "TRAITEUR"]</t>
+          <t>["EAU", "PERRIER", "RED BULL"]</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>dffbd7228ef97383d8a99eac08a8bdb3bdeb12ee78ae43181baed195c5979ac7</t>
+          <t>c4a7eb44d75a6042440a82c9a3be149d5fd5466fd4fd86499b63d8f8c209b6b0</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>["EAU", "PERRIER", "RED BULL"]</t>
+          <t>["EVIAN", "SOUVENIR", "SPRAY FACIAL"]</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>c4a7eb44d75a6042440a82c9a3be149d5fd5466fd4fd86499b63d8f8c209b6b0</t>
+          <t>969f4c522c5d2c9d2d32770ccf9792af2a2fca30f1772224b79214a34b3474b5</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>["EVIAN", "SOUVENIR", "SPRAY FACIAL"]</t>
+          <t>["FLOCONS DE MEGEVE", "MERINGUES MYRTILLES", "PERRIER"]</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>969f4c522c5d2c9d2d32770ccf9792af2a2fca30f1772224b79214a34b3474b5</t>
+          <t>073dfc3f9a534773091322baadf83ea79d958ebc6100d88c82742a955618abe1</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>["FLOCONS DE MEGEVE", "MERINGUES MYRTILLES", "PERRIER"]</t>
+          <t>["FRAISE TAGADA", "LIMONADE", "SANDWICH"]</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>073dfc3f9a534773091322baadf83ea79d958ebc6100d88c82742a955618abe1</t>
+          <t>fc945e68ee84fdabdc1bde2daf8d2853e268ba3c9e7af62ee470890e060f8ce5</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>["FRAISE TAGADA", "LIMONADE", "SANDWICH"]</t>
+          <t>["GEL HYDROALCOOLIQUE", "NUXE", "PARFUM"]</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>fc945e68ee84fdabdc1bde2daf8d2853e268ba3c9e7af62ee470890e060f8ce5</t>
+          <t>742457e708d1519c0a4bbb94a7a86d9a07e962a916ac321637155d8cc4f6f779</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>["GEL HYDROALCOOLIQUE", "NUXE", "PARFUM"]</t>
+          <t>["GOURDE", "ISOTHERME", "PARAPLUIE"]</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>742457e708d1519c0a4bbb94a7a86d9a07e962a916ac321637155d8cc4f6f779</t>
+          <t>4c4ec890ba966c22b160bb971715ef7c37cf2e180077e6738004546bdf7f6749</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>["GOURDE", "ISOTHERME", "PARAPLUIE"]</t>
+          <t>["HYGIENE FEMININE", "SALADE BOWL", "SERVIETTES LOVE"]</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>4c4ec890ba966c22b160bb971715ef7c37cf2e180077e6738004546bdf7f6749</t>
+          <t>51057b74e7efa59329f5c5c66155df2bd80d62ff2289c4e51e0a3aa0ef9a0494</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>["HYGIENE FEMININE", "SALADE BOWL", "SERVIETTES LOVE"]</t>
+          <t>["JUS", "OASIS", "RED BULL"]</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>51057b74e7efa59329f5c5c66155df2bd80d62ff2289c4e51e0a3aa0ef9a0494</t>
+          <t>38f947f667f622ac3ca81ff914f3dd4ed1b86de36aa8ea07e868ad58ed1e1ee3</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>["JUS", "OASIS", "RED BULL"]</t>
+          <t>["LIMONADE", "OASIS", "SPRITE"]</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>38f947f667f622ac3ca81ff914f3dd4ed1b86de36aa8ea07e868ad58ed1e1ee3</t>
+          <t>56bf3038276652a37900faaf0626b91464e684ceb29570b7ec4a19a45708e44a</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>["LIMONADE", "OASIS", "SPRITE"]</t>
+          <t>["MERINGUES MYRTILLES", "MIEL", "PATES"]</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>56bf3038276652a37900faaf0626b91464e684ceb29570b7ec4a19a45708e44a</t>
+          <t>bf3f907cf39867aad9f7b3adffc74a45132299cf499e0c5eab81e5419cb0da95</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>["MERINGUES MYRTILLES", "MIEL", "PATES"]</t>
+          <t>["MPG HOUMOUS", "PONCHO", "PORTE CLE"]</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>bf3f907cf39867aad9f7b3adffc74a45132299cf499e0c5eab81e5419cb0da95</t>
+          <t>505bcdd873dabf4787bd0975bcf291b2e74a2dd4aca116718406b1788e4ba50e</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>["MPG HOUMOUS", "PONCHO", "PORTE CLE"]</t>
+          <t>["MPG HOUMOUS", "SALADE BOWL", "SANDWICH"]</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>505bcdd873dabf4787bd0975bcf291b2e74a2dd4aca116718406b1788e4ba50e</t>
+          <t>3edba88c10fb0d8a2a60251b8da5d8d1a69a601d94472f4f92010b97222a6638</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>["MPG HOUMOUS", "SALADE BOWL", "SANDWICH"]</t>
+          <t>["NUXE", "PONCHO", "PRESERVATIF"]</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>3edba88c10fb0d8a2a60251b8da5d8d1a69a601d94472f4f92010b97222a6638</t>
+          <t>7e2c8286b7361a097975a969c822424224444dce97965383a50e797bc7dda168</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>["NUXE", "PONCHO", "PRESERVATIF"]</t>
+          <t>["PATES", "SALADE BOWL", "SANDWICH"]</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>7e2c8286b7361a097975a969c822424224444dce97965383a50e797bc7dda168</t>
+          <t>377fddde6c3a13c9d604fa9947730c346a2233f02a2c12e8ff4db53f6e5e43ed</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>["PATES", "SALADE BOWL", "SANDWICH"]</t>
+          <t>["PETIT SAUCISSON", "POICAMOLE", "SOUPE"]</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>377fddde6c3a13c9d604fa9947730c346a2233f02a2c12e8ff4db53f6e5e43ed</t>
+          <t>b95be7199357113631eb3e3c83ecbeb831e84aa2da56d24cd8044ec955fd5315</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>["PETIT SAUCISSON", "POICAMOLE", "SOUPE"]</t>
+          <t>["PLAT", "RED BULL", "SOUPE"]</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>b95be7199357113631eb3e3c83ecbeb831e84aa2da56d24cd8044ec955fd5315</t>
+          <t>72e9dda396b4bb945ee428a12b32a3753bef7955eb61244eed08d37d49190a0a</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>["PLAT", "RED BULL", "SOUPE"]</t>
+          <t>["PONCHO", "PORTE CLE", "PRESERVATIF"]</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>72e9dda396b4bb945ee428a12b32a3753bef7955eb61244eed08d37d49190a0a</t>
+          <t>f18568e728843de4d4a2fea21104df4462d5960b5ba85e8928d33c11473ab42d</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>["PONCHO", "PORTE CLE", "PRESERVATIF"]</t>
+          <t>["ADAPTATEUR", "GOURDE", "ISOTHERME", "PARAPLUIE"]</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>f18568e728843de4d4a2fea21104df4462d5960b5ba85e8928d33c11473ab42d</t>
+          <t>3ad9a0fde553286885ac49b8793d74cd3a8a713eaa0ed033f1e551f9a004a25e</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>["ADAPTATEUR", "GOURDE", "ISOTHERME", "PARAPLUIE"]</t>
+          <t>["ANTI MOUSTIQUE", "DEODORANT", "HYGIENE FEMININE", "PARAPLUIE"]</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>3ad9a0fde553286885ac49b8793d74cd3a8a713eaa0ed033f1e551f9a004a25e</t>
+          <t>6ca29997011c691056eca1c7a4e012f49806d20b1ddea19e8128e9a2ee2f4dea</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>["ANTI MOUSTIQUE", "DEODORANT", "HYGIENE FEMININE", "PARAPLUIE"]</t>
+          <t>["APERITIF SALE", "BISCUIT", "CHIPS", "PATES"]</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>6ca29997011c691056eca1c7a4e012f49806d20b1ddea19e8128e9a2ee2f4dea</t>
+          <t>3aa09adeea4187c6a1383982b1b3b7fe5845a7105e66a33b61159b9576343cb8</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>["APERITIF SALE", "BISCUIT", "CHIPS", "PATES"]</t>
+          <t>["APERITIF SALE", "CARTE POSTALE", "MIEL", "PATES"]</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>3aa09adeea4187c6a1383982b1b3b7fe5845a7105e66a33b61159b9576343cb8</t>
+          <t>948702b0da8ec7324f6ab2655be02663bfa0ac14b926a8cbbc0b4fbbe9b178c8</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>["APERITIF SALE", "CARTE POSTALE", "MIEL", "PATES"]</t>
+          <t>["APERITIF SALE", "CARTE POSTALE", "PATES", "TROUSSE"]</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>948702b0da8ec7324f6ab2655be02663bfa0ac14b926a8cbbc0b4fbbe9b178c8</t>
+          <t>9a1d29462e7d2b846c39239eced388fd636668489ff7ba6c4d2521cfb6f8686d</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>["APERITIF SALE", "CARTE POSTALE", "PATES", "TROUSSE"]</t>
+          <t>["APERITIF SALE", "MIEL", "PATES", "PELUCHE"]</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>9a1d29462e7d2b846c39239eced388fd636668489ff7ba6c4d2521cfb6f8686d</t>
+          <t>bc72014bdfe2501d9e1ec297f1b5dc56681084fe88cfbb0116775b9d6e689109</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>["APERITIF SALE", "MIEL", "PATES", "PELUCHE"]</t>
+          <t>["ASSORTIMENT DE GUIMAUVE", "CHIPS", "FLOCONS DE MEGEVE", "GRAINES"]</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>bc72014bdfe2501d9e1ec297f1b5dc56681084fe88cfbb0116775b9d6e689109</t>
+          <t>356fbed74485253e7d5563e233983cf0b7828d4e4bbe444f12ad6fffc513cde0</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>["ASSORTIMENT DE GUIMAUVE", "CHIPS", "FLOCONS DE MEGEVE", "GRAINES"]</t>
+          <t>["ASSORTIMENT DE GUIMAUVE", "CONFISERIE", "DESSERT", "PATES"]</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>356fbed74485253e7d5563e233983cf0b7828d4e4bbe444f12ad6fffc513cde0</t>
+          <t>00357edb87f84cbf7e9c991fd99c5babe0dced19f71c6654f903f8892a5fc487</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>["ASSORTIMENT DE GUIMAUVE", "CONFISERIE", "DESSERT", "PATES"]</t>
+          <t>["ASSORTIMENT DE GUIMAUVE", "FLOCONS DE MEGEVE", "GRAINES", "MINI TABLETTES"]</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>00357edb87f84cbf7e9c991fd99c5babe0dced19f71c6654f903f8892a5fc487</t>
+          <t>df5244de9e7669251dc087779e10e13f4485821205e9e1a8d04768164776d521</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>["ASSORTIMENT DE GUIMAUVE", "FLOCONS DE MEGEVE", "GRAINES", "MINI TABLETTES"]</t>
+          <t>["BAIES DE GOJI", "BISCUIT", "CAFE CHOCOLAT", "PATES"]</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>df5244de9e7669251dc087779e10e13f4485821205e9e1a8d04768164776d521</t>
+          <t>6c1ca8e30ca4195cc7959c7526e1ca1844b08b5d180ff443c13a1afb8d4e85ad</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>["BAIES DE GOJI", "BISCUIT", "CAFE CHOCOLAT", "PATES"]</t>
+          <t>["BAIES DE GOJI", "CAFE CHOCOLAT", "CHOCOLAT", "YAOURT"]</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>6c1ca8e30ca4195cc7959c7526e1ca1844b08b5d180ff443c13a1afb8d4e85ad</t>
+          <t>ff074f0c6eb00d65726fd290e326319b9e2a6388c3f6b0f451b1cf18409aaaf0</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>["BAIES DE GOJI", "CAFE CHOCOLAT", "CHOCOLAT", "YAOURT"]</t>
+          <t>["BAIES DE GOJI", "CHOCOLAT", "TRAITEUR", "YAOURT"]</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>ff074f0c6eb00d65726fd290e326319b9e2a6388c3f6b0f451b1cf18409aaaf0</t>
+          <t>d060ba0685f1c9e06496edb1a5d9ba03364adeaa55576d6be41ea91aae25774b</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>["BAIES DE GOJI", "CHOCOLAT", "TRAITEUR", "YAOURT"]</t>
+          <t>["BALLE DE MASSAGE", "BONNET", "GANTS", "TOUR DE COU"]</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>d060ba0685f1c9e06496edb1a5d9ba03364adeaa55576d6be41ea91aae25774b</t>
+          <t>501c79418a1ff9590ba927ea87775b32a212530697f4a49c318b71cd94317b33</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>["BALLE DE MASSAGE", "BONNET", "GANTS", "TOUR DE COU"]</t>
+          <t>["BAM CO", "BARRE", "GULA", "SNICKERS"]</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>501c79418a1ff9590ba927ea87775b32a212530697f4a49c318b71cd94317b33</t>
+          <t>62b9d241fa31807aa9cebd7a1626736c827063d3fdc0a4fc4c0855c452dd9c2a</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>["BAM CO", "BARRE", "GULA", "SNICKERS"]</t>
+          <t>["BAM CO", "BARRE", "RED BULL", "SNICKERS"]</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>62b9d241fa31807aa9cebd7a1626736c827063d3fdc0a4fc4c0855c452dd9c2a</t>
+          <t>f8203b376fe113d776c9f1b359cd69bc7541b725a9dcce0c0fc95cf9d66ff246</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>["BAM CO", "BARRE", "RED BULL", "SNICKERS"]</t>
+          <t>["BAM CO", "CHIPS", "GULA", "SALADE BOWL"]</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>f8203b376fe113d776c9f1b359cd69bc7541b725a9dcce0c0fc95cf9d66ff246</t>
+          <t>26f18c6ddca744b6f2f7d765b77a1e5749d64d4013c1ab26f312daca6da642f0</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>["BAM CO", "CHIPS", "GULA", "SALADE BOWL"]</t>
+          <t>["BARQUETTE DE FRAISE", "CHOCOLAT", "CONFITURE", "CRUNCH"]</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>26f18c6ddca744b6f2f7d765b77a1e5749d64d4013c1ab26f312daca6da642f0</t>
+          <t>b86b32621343d56a1e698818aeddb10af2fd993dba97835e8baf81d4f2856e7a</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>["BARQUETTE DE FRAISE", "CHOCOLAT", "CONFITURE", "CRUNCH"]</t>
+          <t>["BARQUETTE DE FRAISE", "CONFITURE", "PLAT", "POICAMOLE"]</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>b86b32621343d56a1e698818aeddb10af2fd993dba97835e8baf81d4f2856e7a</t>
+          <t>67b428277ed39bb8fb48ced84d414028314e58a956cacd031f8398fbdf2a4da5</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>["BARQUETTE DE FRAISE", "CONFITURE", "PLAT", "POICAMOLE"]</t>
+          <t>["BARQUETTE DE FRAISE", "CONFITURE", "POICAMOLE", "SOUPE"]</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>67b428277ed39bb8fb48ced84d414028314e58a956cacd031f8398fbdf2a4da5</t>
+          <t>e42f829f0586ed983dc7c95e60ef670887e0c4ab2b19894d70ef690455c494f7</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>["BARQUETTE DE FRAISE", "CONFITURE", "POICAMOLE", "SOUPE"]</t>
+          <t>["BARRE", "BAUME LEVRES", "BISCUIT", "GRAINES"]</t>
         </is>
       </c>
     </row>
